--- a/data/eddy/output/eddy_gto.xlsx
+++ b/data/eddy/output/eddy_gto.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,9 +35,6 @@
       <sz val="18"/>
     </font>
     <font>
-      <color rgb="007F6000"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00333333"/>
       <sz val="12"/>
@@ -51,8 +48,20 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="FF9C0006"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="007F6000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,14 +70,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
-        <bgColor rgb="004F81BD"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,31 +114,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -489,7 +516,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -522,7 +549,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
@@ -534,7 +561,7 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>-7.4</v>
       </c>
     </row>
@@ -544,7 +571,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Eddy after RLX 1 on block (-11)</t>
         </is>
@@ -553,96 +580,96 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Eddy</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.8148148148148148</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="4" t="n">
         <v>-7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Eddy</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.1851851851851852</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="4" t="n">
         <v>-7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="11" t="n">
         <v>0.7037037037037037</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>ws44</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="11" t="n">
         <v>0.2962962962962963</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="5" t="n">
         <v>7</v>
       </c>
     </row>
@@ -664,7 +691,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
@@ -697,7 +724,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
@@ -709,7 +736,7 @@
           <t>Payoff</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>8.199999999999999</v>
       </c>
     </row>
@@ -719,7 +746,7 @@
           <t>Comment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Eddy into RLX at +6 </t>
         </is>
@@ -728,204 +755,204 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>strategy_value</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Eddy</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>RLX.1+2</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.249882800291697</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Eddy</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>RLX.2</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.1460699031149078</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Eddy</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>RLX.3</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.02664340035420356</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Eddy</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>RLX.3,3</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>0.1760079174914053</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Eddy</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>RLX.4,3</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <v>0.4013959787477862</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="11" t="n">
         <v>0.3520339213575488</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="5" t="n">
         <v>-8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="11" t="n">
         <v>0.1022538516743642</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="5" t="n">
         <v>-8</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>SSL</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="11" t="n">
         <v>0.03047481797872464</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="5" t="n">
         <v>-8</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Power Crush</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="11" t="n">
         <v>0.3519080401893716</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="5" t="n">
         <v>-8</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Reina</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Hop Kick</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="11" t="n">
         <v>0.1633293687999907</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="5" t="n">
         <v>-8</v>
       </c>
     </row>
